--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45099</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45708</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45946</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24227-2022</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44725</v>
+        <v>45335</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 24227-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>44725</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 24227-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45335</v>
+        <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24227-2022</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44725</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45946</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45099</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45708</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45946</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45099</v>
+        <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45006</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45946</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45195</v>
+        <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45006</v>
+        <v>45708</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45946</v>
+        <v>45313</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45006</v>
+        <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45708</v>
+        <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45006</v>
+        <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45946</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45946</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45335</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45708</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45946</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45335</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45195</v>
+        <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45006</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45708</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45946</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45099</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45946</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45708</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45313</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45006</v>
+        <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45708</v>
+        <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45195</v>
+        <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45006</v>
+        <v>45708</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45708</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45946</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45708</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45946</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45708</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45946</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45006</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45708</v>
+        <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45195</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45195</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45006</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45099</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45946</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45703</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45099</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45708</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45946</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45006</v>
+        <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45313</v>
+        <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45703</v>
+        <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45708</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45946</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45195</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45708</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45946</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45708</v>
+        <v>45099</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45313</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45099</v>
+        <v>45195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45708</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45946</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45195</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45335</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45335</v>
+        <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45703</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45335</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45946</v>
+        <v>45099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45703</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45335</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45195</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45708</v>
+        <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45703</v>
+        <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45195</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45335</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45195</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>45703</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45335</v>
+        <v>45703</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45195</v>
+        <v>45313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>45708</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>45946</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45313</v>
+        <v>45335</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45703</v>
+        <v>45195</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45099</v>
+        <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 2593-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45703</v>
+        <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2593-2024</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45313</v>
+        <v>45703</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45708</v>
+        <v>45335</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,14 +1210,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45946</v>
+        <v>45195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45335</v>
+        <v>45099</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45195</v>
+        <v>45708</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45099</v>
+        <v>45946</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 8194-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45703</v>
+        <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45335</v>
+        <v>45946</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45195</v>
+        <v>45099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45099</v>
+        <v>45703</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8194-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45708</v>
+        <v>45335</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45006</v>
+        <v>45195</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45946</v>
+        <v>45006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt HELSINGBORG.xlsx
+++ b/Översikt HELSINGBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45005</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45147</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44641</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>44725</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50997-2025</t>
+          <t>A 5792-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45946</v>
+        <v>45335</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28288-2023</t>
+          <t>A 45832-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45099</v>
+        <v>45195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7333-2025</t>
+          <t>A 50997-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,14 +1283,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45703</v>
+        <v>45946</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5792-2024</t>
+          <t>A 13651-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45335</v>
+        <v>45006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45832-2023</t>
+          <t>A 28288-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45195</v>
+        <v>45099</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13651-2023</t>
+          <t>A 7333-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45006</v>
+        <v>45703</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
